--- a/Zoomlion/ZA14J.xlsx
+++ b/Zoomlion/ZA14J.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,33 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E497"/>
+  <dimension ref="A1:F497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Код материалов</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Наименование и спецификация</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Models</t>
         </is>
       </c>
     </row>
@@ -454,8 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Опора кольцевого 
-предохранителя</t>
+          <t>Опора кольцевого предохранителя</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -464,6 +480,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,6 +506,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -506,6 +532,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -527,6 +558,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -548,6 +584,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -560,10 +601,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Монтажная 
-панель 
-водяного 
-бака</t>
+          <t>Монтажная панель водяного бака</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -572,6 +610,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -593,6 +636,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -614,6 +662,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -635,6 +688,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -656,6 +714,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -677,6 +740,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -698,6 +766,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -719,6 +792,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -740,6 +818,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -761,6 +844,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -782,6 +870,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -803,6 +896,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -824,6 +922,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -845,6 +948,11 @@
           <t>Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -866,6 +974,11 @@
           <t>Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -887,6 +1000,11 @@
           <t>Впускная система 00773400108000000</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -908,6 +1026,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -929,6 +1052,11 @@
           <t>Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -950,6 +1078,11 @@
           <t>Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -962,7 +1095,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Перегородка Ⅰ</t>
+          <t>Перегородка I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -971,6 +1104,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -992,6 +1130,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1004,9 +1147,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Свариваемые 
-изделия 
-платформы</t>
+          <t>Свариваемые изделия платформы</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1015,6 +1156,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1036,6 +1182,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1057,6 +1208,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1078,6 +1234,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1099,6 +1260,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1111,9 +1277,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Сварная 
-деталь 
-кронштейна</t>
+          <t>Сварная деталь кронштейна</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1122,6 +1286,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1134,7 +1303,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Анкерная плита Ⅱ</t>
+          <t>Анкерная плита II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1143,6 +1312,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1164,6 +1338,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1185,6 +1364,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1206,6 +1390,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1227,6 +1416,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1248,6 +1442,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1269,6 +1468,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1290,6 +1494,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1311,6 +1520,11 @@
           <t>Консоль 00773400210000000; Верхняя стрела в сборе 00773400300000000; Башенная стрела в сборе 00773400400000000; Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1332,6 +1546,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1353,6 +1572,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1374,6 +1598,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1395,6 +1624,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1416,6 +1650,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1437,6 +1676,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1458,6 +1702,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1479,6 +1728,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1491,7 +1745,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Штифт Ⅱ</t>
+          <t>Штифт II</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1500,6 +1754,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1521,6 +1780,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1542,6 +1806,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1563,6 +1832,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1584,6 +1858,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1605,6 +1884,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1626,6 +1910,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1647,6 +1936,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1668,6 +1962,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1680,7 +1979,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Регулировочная шайба Ⅱ</t>
+          <t>Регулировочная шайба II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1689,6 +1988,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1701,7 +2005,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Регулировочная шайба Ⅲ</t>
+          <t>Регулировочная шайба III</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1710,6 +2014,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1731,6 +2040,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1743,7 +2057,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Регулировочная шайба Ⅴ</t>
+          <t>Регулировочная шайба V</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1752,6 +2066,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1764,7 +2083,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Регулировочная шайба Ⅵ</t>
+          <t>Регулировочная шайба VI</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1773,6 +2092,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1785,12 +2109,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Боковая 
-подпирающая 
-плита 
-гидроцилиндра 
-выдвижения-
-втягивания</t>
+          <t>Боковая подпирающая плита гидроцилиндра выдвижения- втягивания</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -1799,6 +2118,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1811,7 +2135,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Штифт Ⅴ</t>
+          <t>Штифт V</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -1820,6 +2144,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1841,6 +2170,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1862,6 +2196,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1883,6 +2222,11 @@
           <t>Верхняя стрела в сборе 00773400300000000; Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1904,6 +2248,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1916,10 +2265,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Контактная 
-плата 
-концевого 
-выключателя</t>
+          <t>Контактная плата концевого выключателя</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -1928,6 +2274,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1940,10 +2291,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Правая 
-контактная 
-плата 
-концевого выключателя</t>
+          <t>Правая контактная плата концевого выключателя</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -1952,6 +2300,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1973,6 +2326,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1994,6 +2352,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2006,10 +2369,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Кожух 
-селекторного 
-клапана 
-платформы</t>
+          <t>Кожух селекторного клапана платформы</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2018,6 +2378,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2030,11 +2395,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Подпирающая 
-плита 
-гидроцилиндра 
-выдвижения-
-втягивания</t>
+          <t>Подпирающая плита гидроцилиндра выдвижения- втягивания</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2043,6 +2404,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2064,6 +2430,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2085,6 +2456,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2097,8 +2473,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Гидроцилиндр изменения 
-вылета основной стрелы</t>
+          <t>Гидроцилиндр изменения вылета основной стрелы</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2107,6 +2482,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2119,8 +2499,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Нижний гидроцилиндр 
-выравнивания</t>
+          <t>Нижний гидроцилиндр выравнивания</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2129,6 +2508,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2141,8 +2525,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Верхний гидроцилиндр 
-выравнивания</t>
+          <t>Верхний гидроцилиндр выравнивания</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2151,6 +2534,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2163,9 +2551,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Гидроцилиндр 
-выдвижения-
-втягивания</t>
+          <t>Гидроцилиндр выдвижения- втягивания</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2174,6 +2560,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2195,6 +2586,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2216,6 +2612,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2237,6 +2638,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2258,6 +2664,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2279,6 +2690,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2300,6 +2716,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2321,6 +2742,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2342,6 +2768,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2363,6 +2794,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2384,6 +2820,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2405,6 +2846,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2426,6 +2872,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2447,6 +2898,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2468,6 +2924,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2489,6 +2950,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2510,6 +2976,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2531,6 +3002,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2552,6 +3028,11 @@
           <t>Башенная стрела в сборе 00773400400000000; Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2573,6 +3054,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2594,6 +3080,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2615,6 +3106,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2636,6 +3132,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2657,6 +3158,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2669,8 +3175,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Буферная  плита  основной 
-стрелы</t>
+          <t>Буферная  плита  основной стрелы</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -2679,6 +3184,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2700,6 +3210,11 @@
           <t>Верхняя стрела в сборе 00773400300000000; Башенная стрела в сборе 00773400400000000; Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2721,6 +3236,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2742,6 +3262,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2763,6 +3288,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2784,6 +3314,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2805,6 +3340,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2817,9 +3357,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Прижимная 
-резиновая 
-планка</t>
+          <t>Прижимная резиновая планка</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -2828,6 +3366,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2849,6 +3392,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2861,9 +3409,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Верхняя 
-прижимная 
-планка</t>
+          <t>Верхняя прижимная планка</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -2872,6 +3418,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2884,9 +3435,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Нижняя 
-прижимная 
-планка</t>
+          <t>Нижняя прижимная планка</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -2895,6 +3444,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2916,6 +3470,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2937,6 +3496,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2958,6 +3522,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2979,6 +3548,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3000,6 +3574,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3012,8 +3591,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Нажимной  рычаг  нижней 
-башенной стрелы</t>
+          <t>Нажимной  рычаг  нижней башенной стрелы</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3022,6 +3600,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3034,10 +3617,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Тяга 
-нижней 
-башенной 
-стрелы</t>
+          <t>Тяга нижней башенной стрелы</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -3046,6 +3626,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3058,10 +3643,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Тяга 
-верхней 
-башенной 
-стрелы</t>
+          <t>Тяга верхней башенной стрелы</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -3070,6 +3652,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3082,8 +3669,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Нажимной  рычаг  верхней 
-башенной стрелы</t>
+          <t>Нажимной  рычаг  верхней башенной стрелы</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3092,6 +3678,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3113,6 +3704,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3125,9 +3721,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Гидроцилиндр 
-башенной 
-стрелы</t>
+          <t>Гидроцилиндр башенной стрелы</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -3136,6 +3730,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3157,6 +3756,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3178,6 +3782,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3199,6 +3808,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3220,6 +3834,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3241,6 +3860,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3262,6 +3886,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3283,6 +3912,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3304,6 +3938,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3325,6 +3964,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3346,6 +3990,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3367,6 +4016,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3379,8 +4033,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Нижний штифт башенной 
-стрелы</t>
+          <t>Нижний штифт башенной стрелы</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -3389,6 +4042,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3410,6 +4068,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3431,6 +4094,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3443,9 +4111,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Подушка 
-башенной 
-стрелы; Подушка башенной стрелы</t>
+          <t>Подушка башенной стрелы</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3454,6 +4120,11 @@
           <t>Башенная стрела в сборе 00773400400000000; Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3475,6 +4146,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3496,6 +4172,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3517,6 +4198,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3538,6 +4224,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3550,8 +4241,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Установочное гнездо путевого 
-выключателя</t>
+          <t>Установочное гнездо путевого выключателя</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -3560,6 +4250,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3581,6 +4276,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3602,6 +4302,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3623,6 +4328,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3644,6 +4354,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3665,6 +4380,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3686,6 +4406,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3707,6 +4432,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3728,6 +4458,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3749,6 +4484,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3761,9 +4501,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Опора шкафа  
-электрического 
-управления</t>
+          <t>Опора шкафа электрического управления</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -3772,6 +4510,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3784,8 +4527,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Опорная плита аварийного 
-насоса</t>
+          <t>Опорная плита аварийного насоса</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -3794,6 +4536,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3815,6 +4562,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3836,6 +4588,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3857,6 +4614,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3878,6 +4640,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3899,6 +4666,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3911,8 +4683,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Опора фильтра гидравлического 
-масла</t>
+          <t>Опора фильтра гидравлического масла</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -3921,6 +4692,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3942,6 +4718,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3963,6 +4744,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3984,6 +4770,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4005,6 +4796,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4026,6 +4822,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4038,10 +4839,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Защитный 
-кожух 
-коробки 
-управления</t>
+          <t>Защитный кожух коробки управления</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -4050,6 +4848,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4071,6 +4874,11 @@
           <t>Балансир 00773401000000000</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4092,6 +4900,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4113,6 +4926,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4134,6 +4952,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4155,6 +4978,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4176,6 +5004,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4188,8 +5021,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Держатель левого шарнира 
-замка</t>
+          <t>Держатель левого шарнира замка</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4198,6 +5030,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4219,6 +5056,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4240,6 +5082,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4261,6 +5108,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4282,6 +5134,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4303,6 +5160,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4324,6 +5186,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4345,6 +5212,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4357,8 +5229,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Шайба штифта поворотной 
-цапфы</t>
+          <t>Шайба штифта поворотной цапфы</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -4367,6 +5238,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4379,10 +5255,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Монтажная 
-панель 
-блок 
-клапанов шасси</t>
+          <t>Монтажная панель блок клапанов шасси</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -4391,6 +5264,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4403,10 +5281,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Направляющий 
-рельс 
-датчика 
-угла</t>
+          <t>Направляющий рельс датчика угла</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -4415,6 +5290,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4427,10 +5307,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Регулировочная 
-шайба 
-направляющего  рельса  датчика 
-угла</t>
+          <t>Регулировочная шайба направляющего  рельса  датчика угла</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -4439,6 +5316,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4451,8 +5333,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Верхняя шайба поворотной 
-цапфы</t>
+          <t>Верхняя шайба поворотной цапфы</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -4461,6 +5342,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4482,6 +5368,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4503,6 +5394,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4524,6 +5420,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4545,6 +5446,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4557,8 +5463,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Опора маслопровода мотора  
-I</t>
+          <t>Опора маслопровода мотора I</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -4567,6 +5472,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4579,8 +5489,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Фиксирующее кольцо 
-маслопровода мотора</t>
+          <t>Фиксирующее кольцо маслопровода мотора</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -4589,6 +5498,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4601,8 +5515,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Опора маслопровода мотора  
-II</t>
+          <t>Опора маслопровода мотора II</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -4611,6 +5524,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4632,6 +5550,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4644,8 +5567,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Сварные изделия переднего 
-моста</t>
+          <t>Сварные изделия переднего моста</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -4654,6 +5576,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4675,6 +5602,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4687,8 +5619,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Поворотная цапфа  
-II</t>
+          <t>Поворотная цапфа II</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -4697,6 +5628,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4718,6 +5654,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4730,8 +5671,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Поворотная цапфа  
-II</t>
+          <t>Поворотная цапфа II</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -4740,6 +5680,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4752,8 +5697,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Гидроцилиндр рулевого 
-управления</t>
+          <t>Гидроцилиндр рулевого управления</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -4762,6 +5706,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4783,6 +5732,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4804,6 +5758,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4825,6 +5784,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4837,21 +5801,18 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Электрический шкаф 
-управления поворотной 
-платформой 1; Электрический шкаф 
-управления поворотной 
-платформой 2; Электрический шкаф 
-управления платформой; Электрический 
-шкаф 
-управления  платформой  в 
-сборе</t>
+          <t>Электрический шкаф управления  платформой  в сборе; Электрический шкаф управления поворотной платформой 1; Электрический шкаф управления поворотной платформой 2; Электрический шкаф управления платформой</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Пучок кабеля поворотной платформы 00773406220410000; Пучок кабеля платформы 00773406220440000 Модификация волочащегося кабеля 00773406200610000; Рабочая платформа 00773400110000000</t>
+          <t>Рабочая платформа 00773400110000000; Пучок кабеля поворотной платформы 00773406220410000; Пучок кабеля платформы 00773406220440000 Модификация волочащегося кабеля 00773406200610000</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -4866,8 +5827,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Пучок кабеля поворотной 
-платформы</t>
+          <t>Пучок кабеля поворотной платформы</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -4876,6 +5836,11 @@
           <t>Пучок кабеля стрелы 00773406200430000</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4897,6 +5862,11 @@
           <t>Пучок кабеля поворотной платформы 00773406220410000</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4909,9 +5879,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Соединительный провод между 
-аккумулятором и пусковым 
-мотором</t>
+          <t>Соединительный провод между аккумулятором и пусковым мотором</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -4920,6 +5888,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4932,10 +5905,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Соединительный провод от 
-отрицательного полюса 
-аккумулятора к ручному 
-переключателю</t>
+          <t>Соединительный провод от отрицательного полюса аккумулятора к ручному переключателю</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -4944,6 +5914,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4956,9 +5931,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Соединительный провод от 
-ручного переключателя к 
-металлизации</t>
+          <t>Соединительный провод от ручного переключателя к металлизации</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -4967,6 +5940,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4979,9 +5957,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Соединительная линия между 
-вспомогательным силовым 
-насосом и предохранителем</t>
+          <t>Соединительная линия между вспомогательным силовым насосом и предохранителем</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -4990,6 +5966,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5002,8 +5983,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Соединительный провод между 
-двигателем и металлизацией</t>
+          <t>Соединительный провод между двигателем и металлизацией</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -5012,6 +5992,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5024,8 +6009,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Соединительный провод между 
-аккумулятором и</t>
+          <t>Соединительный провод между аккумулятором и</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -5034,6 +6018,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5055,6 +6044,11 @@
           <t>Пучок кабеля стрелы 00773406200430000</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5067,8 +6061,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Пучок кабеля поворотной 
-платформы</t>
+          <t>Пучок кабеля поворотной платформы</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5077,6 +6070,11 @@
           <t>ECU 电缆束 00773406220420000</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5098,6 +6096,11 @@
           <t>Пучок кабеля поворотной платформы 00773406220410000</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5119,6 +6122,11 @@
           <t>Пучок кабеля платформы 00773406220440000 Модификация волочащегося кабеля 00773406200610000</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5131,8 +6139,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Соединительный провод между 
-реле и подогревателем</t>
+          <t>Соединительный провод между реле и подогревателем</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -5141,6 +6148,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5162,6 +6174,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5183,6 +6200,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5204,6 +6226,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5225,6 +6252,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5246,6 +6278,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5267,6 +6304,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5288,6 +6330,11 @@
           <t>Впускная система 00773400108000000</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5309,6 +6356,11 @@
           <t>Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5330,6 +6382,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5351,6 +6408,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5372,6 +6434,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5393,6 +6460,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5414,6 +6486,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5435,6 +6512,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5456,6 +6538,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5468,7 +6555,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Гнутая пластина Ⅱ</t>
+          <t>Гнутая пластина II</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -5477,6 +6564,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5498,6 +6590,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5519,6 +6616,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5540,6 +6642,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5561,6 +6668,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5582,6 +6694,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5603,6 +6720,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5624,6 +6746,11 @@
           <t>Впускная система 00773400108000000</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5645,6 +6772,11 @@
           <t>Впускная система 00773400108000000</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5666,6 +6798,11 @@
           <t>Впускная система 00773400108000000</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5687,6 +6824,11 @@
           <t>Впускная система 00773400108000000</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5708,6 +6850,11 @@
           <t>Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5729,6 +6876,11 @@
           <t>Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5750,6 +6902,11 @@
           <t>Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5771,6 +6928,11 @@
           <t>Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5792,6 +6954,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5813,6 +6980,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5834,6 +7006,11 @@
           <t>Впускная система 00773400108000000</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5855,6 +7032,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5876,6 +7058,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5897,6 +7084,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5918,6 +7110,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5939,6 +7136,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5960,6 +7162,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5981,6 +7188,11 @@
           <t>Гидравлический насос в сборе 00773405200400000</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6002,6 +7214,11 @@
           <t>Гидравлический насос в сборе 00773405200400000</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6014,8 +7231,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Аварийный насос с приводом от 
-электродвигателя</t>
+          <t>Аварийный насос с приводом от электродвигателя</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -6024,6 +7240,11 @@
           <t>Сборка аварийного насоса с приводом от электродвигателя 00773405202000000</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6045,6 +7266,11 @@
           <t>Сборка ходового мотора 00773405200600000</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6070,6 +7296,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6082,11 +7313,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Обратный 
-клапан 
-с 
-прямым 
-соединителем</t>
+          <t>Обратный клапан с прямым соединителем</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -6095,6 +7322,11 @@
           <t>Главный клапан в сборе 00773405201600000</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6116,6 +7348,11 @@
           <t>Главный клапан в сборе 00773405201600000</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6137,6 +7374,11 @@
           <t>Сборка селекторного клапана выравнивания 00773405202200000</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6158,6 +7400,11 @@
           <t>Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773405203000000; Балансировочный клапан гидроцилиндра консоли в сборе 00773405203200000</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6179,6 +7426,11 @@
           <t>Сборка ходового делительного клапана 00773405200800000</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6191,9 +7443,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Балансировочный 
-клапан 
-выдвижения-втягивания</t>
+          <t>Балансировочный клапан выдвижения-втягивания</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -6202,6 +7452,11 @@
           <t>Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773405203800000</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6214,13 +7469,18 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Селекторный клапан платформы; Направляющий клапан2</t>
+          <t>Направляющий клапан2; Селекторный клапан платформы</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Селекторный клапан выдвижения-втягивания в сборе 00773405202400000; Селекторный клапан платформы в сборе 00773405201200000</t>
+          <t>Селекторный клапан платформы в сборе 00773405201200000; Селекторный клапан выдвижения-втягивания в сборе 00773405202400000</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -6244,6 +7504,11 @@
           <t>Балансировочный клапан нижнего гидроцилиндра выравнивания в сборе 00773405202800000</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6265,6 +7530,11 @@
           <t>Сборка клапан ходового управления 00773405201000000</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6277,8 +7547,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Весовой  опускающий  клапан  с 
-изменением амплитуды</t>
+          <t>Весовой  опускающий  клапан  с изменением амплитуды</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -6287,6 +7556,11 @@
           <t>Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773405203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773405203600000</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6308,6 +7582,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6329,6 +7608,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6350,6 +7634,11 @@
           <t>Сборка фильтра низкого давления 00773405201400000</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6371,6 +7660,11 @@
           <t>Фильтр высокого давления в сборе 00773405204200000</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6392,6 +7686,11 @@
           <t>Сборка блока маслоканала 00773405202600000</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6413,6 +7712,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6425,8 +7729,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Контроллер двигателя 
-топливного дросселя</t>
+          <t>Контроллер двигателя топливного дросселя</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -6435,6 +7738,11 @@
           <t>ECU 电缆束 00773406220420000</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6447,13 +7755,18 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Аварийный зуммер; Зуммер</t>
+          <t>Зуммер; Аварийный зуммер</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Пучок кабеля поворотной платформы 00773406220410000; Поворотная платформа 00773400830000000</t>
+          <t>Поворотная платформа 00773400830000000; Пучок кабеля поворотной платформы 00773406220410000</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -6468,13 +7781,18 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Реле подогревателя; Контактор постоянного тока</t>
+          <t>Контактор постоянного тока; Реле подогревателя</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>ECU 电缆束 00773406220420000; Питательный провод 00773406220450000; Поворотная платформа 00773400830000000</t>
+          <t>Поворотная платформа 00773400830000000; ECU 电缆束 00773406220420000; Питательный провод 00773406220450000</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -6498,6 +7816,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6519,6 +7842,11 @@
           <t>Пучок кабеля поворотной платформы 00773406220410000</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6531,10 +7859,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Концевой выключатель длины 
-стрелы 2; Концевой выключатель длины 
-стрелы 1; Концевой выключатель угла; Концевой выключатель угла 
-башенной стрелы 1</t>
+          <t>Концевой выключатель длины стрелы 2; Концевой выключатель длины стрелы 1; Концевой выключатель угла; Концевой выключатель угла башенной стрелы 1</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -6543,6 +7868,11 @@
           <t>Пучок кабеля стрелы 00773406200430000</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6561,7 +7891,12 @@
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Пучок кабеля платформы 00773406220440000 Модификация волочащегося кабеля 00773406200610000; Рабочая платформа 00773400110000000</t>
+          <t>Рабочая платформа 00773400110000000; Пучок кабеля платформы 00773406220440000 Модификация волочащегося кабеля 00773406200610000</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -6585,6 +7920,11 @@
           <t>Питательный провод 00773406220450000</t>
         </is>
       </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6606,6 +7946,11 @@
           <t>Пучок кабеля стрелы 00773406200430000</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6624,7 +7969,12 @@
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Пучок кабеля платформы 00773406220440000 Модификация волочащегося кабеля 00773406200610000; Рабочая платформа 00773400110000000</t>
+          <t>Рабочая платформа 00773400110000000; Пучок кабеля платформы 00773406220440000 Модификация волочащегося кабеля 00773406200610000</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -6639,8 +7989,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Двухугольный датчик угла 
-наклона</t>
+          <t>Двухугольный датчик угла наклона</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -6649,6 +7998,11 @@
           <t>Пучок кабеля стрелы 00773406200430000</t>
         </is>
       </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6661,14 +8015,18 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Датчик наклона кузова 
-относительно горизонта; Датчик угла наклона</t>
+          <t>Датчик угла наклона; Датчик наклона кузова относительно горизонта</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Пучок кабеля поворотной платформы 00773406220410000; Поворотная платформа 00773400830000000</t>
+          <t>Поворотная платформа 00773400830000000; Пучок кабеля поворотной платформы 00773406220410000</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -6683,13 +8041,18 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Ручной переключатель; Главный выключатель питания</t>
+          <t>Главный выключатель питания; Ручной переключатель</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Питательный провод 00773406220450000; Поворотная платформа 00773400830000000</t>
+          <t>Поворотная платформа 00773400830000000; Питательный провод 00773406220450000</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -6704,8 +8067,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Положительный полюс 
-аккумулятора</t>
+          <t>Положительный полюс аккумулятора</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -6714,6 +8076,11 @@
           <t>Пучок кабеля поворотной платформы 00773406220410000</t>
         </is>
       </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6726,14 +8093,18 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Концевой выключатель угла 
-поворотной платформы; Концевой выключатель</t>
+          <t>Концевой выключатель; Концевой выключатель угла поворотной платформы</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Пучок кабеля поворотной платформы 00773406220410000; Поворотная платформа 00773400830000000</t>
+          <t>Поворотная платформа 00773400830000000; Пучок кабеля поворотной платформы 00773406220410000</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -6757,6 +8128,11 @@
           <t>Поворотный механизм 00773400900000000</t>
         </is>
       </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6778,6 +8154,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6803,6 +8184,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -6828,6 +8214,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -6853,6 +8244,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -6878,6 +8274,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -6903,6 +8304,11 @@
           <t>Вытяжная система 00773400110000000; Впускная система 00773400108000000; Cистема отвода тепла 00773400106000000; Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -6928,6 +8334,11 @@
           <t>Сборка блока маслоканала 00773405202600000</t>
         </is>
       </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6953,6 +8364,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6978,6 +8394,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7003,6 +8424,11 @@
           <t>Поворотный механизм 00773400900000000</t>
         </is>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7028,6 +8454,11 @@
           <t>Башенная стрела в сборе 00773400400000000; Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7053,6 +8484,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7078,6 +8514,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7103,6 +8544,11 @@
           <t>Верхняя стрела в сборе 00773400300000000; Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7128,6 +8574,11 @@
           <t>Верхняя стрела в сборе 00773400300000000; Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7149,6 +8600,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7174,6 +8630,11 @@
           <t>Консоль 00773400210000000; Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7199,6 +8660,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7224,6 +8690,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7249,6 +8720,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7274,6 +8750,11 @@
           <t>Балансир 00773401000000000</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7299,6 +8780,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7324,6 +8810,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7349,6 +8840,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7374,6 +8870,11 @@
           <t>Сборка фильтра низкого давления 00773405201400000</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7399,6 +8900,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7424,6 +8930,11 @@
           <t>Сборка ходового делительного клапана 00773405200800000</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7449,6 +8960,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7474,6 +8990,11 @@
           <t>Башенная стрела в сборе 00773400400000000; Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7499,6 +9020,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7524,6 +9050,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7549,6 +9080,11 @@
           <t>Верхняя стрела в сборе 00773400300000000; Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7574,6 +9110,11 @@
           <t>Cистема отвода тепла 00773400106000000; Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7599,6 +9140,11 @@
           <t>Верхняя стрела в сборе 00773400300000000; Шасси 00773402810000000; Cистема отвода тепла 00773400106000000; Сборка клапан ходового управления 00773405201000000</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7624,6 +9170,11 @@
           <t>Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773405203000000</t>
         </is>
       </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7649,6 +9200,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7674,6 +9230,11 @@
           <t>Сборка ходового мотора 00773405200600000</t>
         </is>
       </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7699,6 +9260,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7724,6 +9290,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7749,6 +9320,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7774,6 +9350,11 @@
           <t>Башенная стрела в сборе 00773400400000000; Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7799,6 +9380,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7824,6 +9410,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7849,6 +9440,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7874,6 +9470,11 @@
           <t>Башенная стрела в сборе 00773400400000000; Поворотная платформа 00773400830000000; Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7899,6 +9500,11 @@
           <t>Впускная система 00773400108000000; Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7924,6 +9530,11 @@
           <t>Гидравлический насос в сборе 00773405200400000</t>
         </is>
       </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -7949,6 +9560,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -7974,6 +9590,11 @@
           <t>Поворотная платформа 00773400830000000; Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -7999,6 +9620,11 @@
           <t>Балансир 00773401000000000</t>
         </is>
       </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8024,6 +9650,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8049,6 +9680,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8074,6 +9710,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8099,6 +9740,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8124,6 +9770,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8149,6 +9800,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8174,6 +9830,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8199,6 +9860,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8224,6 +9890,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8249,6 +9920,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -8274,6 +9950,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -8299,6 +9980,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -8324,6 +10010,11 @@
           <t>Поворотная платформа 00773400830000000; Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -8349,6 +10040,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8374,6 +10070,11 @@
           <t>Поворотная платформа 00773400830000000; Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8399,6 +10100,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8424,6 +10130,11 @@
           <t>Капот 00773401100000000; Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8445,6 +10156,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8457,8 +10173,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Болт для ограничителя 
-открывания двери M10×70</t>
+          <t>Болт для ограничителя открывания двери M10×70</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -8467,6 +10182,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8492,6 +10212,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8517,6 +10242,11 @@
           <t>Сборка блока маслоканала 00773405202600000; Балансировочный клапан нижнего гидроцилиндра выравнивания в сборе 00773405202800000</t>
         </is>
       </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8542,6 +10272,11 @@
           <t>Селекторный клапан выдвижения-втягивания в сборе 00773405202400000</t>
         </is>
       </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8567,6 +10302,11 @@
           <t>Главный клапан в сборе 00773405201600000</t>
         </is>
       </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8592,6 +10332,11 @@
           <t>Фильтр высокого давления в сборе 00773405204200000</t>
         </is>
       </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8617,6 +10362,11 @@
           <t>Балансировочный клапан гидроцилиндра консоли в сборе 00773405203200000; Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773405203800000</t>
         </is>
       </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8642,6 +10392,11 @@
           <t>Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773405203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773405203600000</t>
         </is>
       </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -8667,6 +10422,11 @@
           <t>Гидравлический насос в сборе 00773405200400000</t>
         </is>
       </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -8692,6 +10452,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -8717,6 +10482,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -8742,6 +10512,11 @@
           <t>Гидравлический бак в сборе 00773405200200000; Сборка аварийного насоса с приводом от электродвигателя 00773405202000000</t>
         </is>
       </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -8767,6 +10542,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -8792,6 +10572,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -8817,6 +10602,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8842,6 +10632,11 @@
           <t>Вытяжная система 00773400110000000</t>
         </is>
       </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8867,6 +10662,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -8892,6 +10692,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -8917,6 +10722,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -8942,6 +10752,11 @@
           <t>Сборка клапан ходового управления 00773405201000000</t>
         </is>
       </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -8967,6 +10782,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8992,6 +10812,11 @@
           <t>Поворотная платформа 00773400830000000; Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -9017,6 +10842,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -9042,6 +10872,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -9067,6 +10902,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -9092,6 +10932,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -9117,6 +10962,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -9129,7 +10979,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Винт M10×50-8,8; Винт M4×50-8.81</t>
+          <t>Винт M4×50-8.81; Винт M10×50-8,8</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -9139,7 +10989,12 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Сборка селекторного клапана выравнивания 00773405202200000; Селекторный клапан платформы в сборе 00773405201200000</t>
+          <t>Селекторный клапан платформы в сборе 00773405201200000; Сборка селекторного клапана выравнивания 00773405202200000</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -9167,6 +11022,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -9192,6 +11052,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -9217,6 +11082,11 @@
           <t>Поворотная платформа 00773400830000000; Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -9242,6 +11112,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -9267,6 +11142,11 @@
           <t>Башенная стрела в сборе 00773400400000000; Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -9292,6 +11172,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -9317,6 +11202,11 @@
           <t>Вытяжная система 00773400110000000; Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -9342,6 +11232,11 @@
           <t>Буксирная система 00773400700000000; Впускная система 00773400108000000; Cистема топлива 00773400104000000; Сборка клапан ходового управления 00773405201000000</t>
         </is>
       </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -9367,6 +11262,11 @@
           <t>Консоль 00773400210000000</t>
         </is>
       </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -9392,6 +11292,11 @@
           <t>Буксирная система 00773400700000000; Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -9417,6 +11322,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -9442,6 +11352,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -9467,6 +11382,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -9492,6 +11412,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -9517,6 +11442,11 @@
           <t>Верхняя стрела в сборе 00773400300000000; Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -9542,6 +11472,11 @@
           <t>Поворотная платформа 00773400830000000; Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -9567,6 +11502,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -9592,6 +11532,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -9617,6 +11562,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -9634,12 +11584,17 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>GB/T889.1-2015; JB/T889.1</t>
+          <t>JB/T889.1; GB/T889.1-2015</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Сборка блока маслоканала 00773405202600000; Башенная стрела в сборе 00773400400000000; Шасси 00773402810000000</t>
+          <t>Башенная стрела в сборе 00773400400000000; Шасси 00773402810000000; Сборка блока маслоканала 00773405202600000</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -9667,6 +11622,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -9692,6 +11652,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9717,6 +11682,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -9742,6 +11712,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -9767,6 +11742,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -9792,6 +11772,11 @@
           <t>Гидравлический насос в сборе 00773405200400000; Сборка ходового мотора 00773405200600000</t>
         </is>
       </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -9814,7 +11799,12 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Сборка селекторного клапана выравнивания 00773405202200000; Селекторный клапан выдвижения-втягивания в сборе 00773405202400000; Селекторный клапан платформы в сборе 00773405201200000</t>
+          <t>Селекторный клапан платформы в сборе 00773405201200000; Сборка селекторного клапана выравнивания 00773405202200000; Селекторный клапан выдвижения-втягивания в сборе 00773405202400000</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -9842,6 +11832,11 @@
           <t>Главный клапан в сборе 00773405201600000</t>
         </is>
       </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -9867,6 +11862,11 @@
           <t>Поворотный механизм 00773400900000000</t>
         </is>
       </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -9888,6 +11888,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -9913,6 +11918,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -9938,6 +11948,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -9955,12 +11970,17 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>JB/T97.1; GB/T97.1-2002</t>
+          <t>GB/T97.1-2002; JB/T97.1</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773400830000000; Капот 00773401100000000; Рабочая платформа 00773400110000000</t>
+          <t>Рабочая платформа 00773400110000000; Поворотная платформа 00773400830000000; Капот 00773401100000000</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -9985,7 +12005,12 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Двигатель 00773400102000000; Рабочая платформа 00773400110000000</t>
+          <t>Рабочая платформа 00773400110000000; Двигатель 00773400102000000</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -10013,6 +12038,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -10038,6 +12068,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -10063,6 +12098,11 @@
           <t>Башенная стрела в сборе 00773400400000000; Гидравлический бак в сборе 00773405200200000; Сборка аварийного насоса с приводом от электродвигателя 00773405202000000</t>
         </is>
       </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -10088,6 +12128,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -10105,12 +12150,17 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>JB/T93-1987; JB/T93</t>
+          <t>JB/T93; JB/T93-1987</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Балансировочный клапан нижнего гидроцилиндра выравнивания в сборе 00773405202800000; Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773405203000000; Балансировочный клапан гидроцилиндра консоли в сборе 00773405203200000; Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773405203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773405203600000; Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773405203800000; Фильтр высокого давления в сборе 00773405204200000; Буксирная система 00773400700000000; Гидравлический бак в сборе 00773405200200000</t>
+          <t>Буксирная система 00773400700000000; Гидравлический бак в сборе 00773405200200000; Балансировочный клапан нижнего гидроцилиндра выравнивания в сборе 00773405202800000; Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773405203000000; Балансировочный клапан гидроцилиндра консоли в сборе 00773405203200000; Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773405203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773405203600000; Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773405203800000; Фильтр высокого давления в сборе 00773405204200000</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -10135,7 +12185,12 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Балансир 00773401000000000; Рабочая платформа 00773400110000000</t>
+          <t>Рабочая платформа 00773400110000000; Балансир 00773401000000000</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -10155,13 +12210,17 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>GB/T97.1-2002; JB/T97.1; GB/T97.1-2002  8-
-200HV</t>
+          <t>GB/T97.1-2002; JB/T97.1; GB/T97.1-2002  8- 200HV</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Фильтр высокого давления в сборе 00773405204200000; Буксирная система 00773400700000000; Вытяжная система 00773400110000000; Впускная система 00773400108000000; Cистема отвода тепла 00773400106000000; Cистема топлива 00773400104000000; Рабочая платформа 00773400110000000</t>
+          <t>Рабочая платформа 00773400110000000; Буксирная система 00773400700000000; Вытяжная система 00773400110000000; Впускная система 00773400108000000; Cистема отвода тепла 00773400106000000; Cистема топлива 00773400104000000; Фильтр высокого давления в сборе 00773405204200000</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -10189,6 +12248,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -10214,6 +12278,11 @@
           <t>Балансир 00773401000000000</t>
         </is>
       </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -10239,6 +12308,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -10264,6 +12338,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -10289,6 +12368,11 @@
           <t>Башенная стрела в сборе 00773400400000000; Двигатель 00773400102000000; Сборка аварийного насоса с приводом от электродвигателя 00773405202000000</t>
         </is>
       </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -10311,7 +12395,12 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Шасси 00773402810000000; Рабочая платформа 00773400110000000</t>
+          <t>Рабочая платформа 00773400110000000; Шасси 00773402810000000</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -10339,6 +12428,11 @@
           <t>Двигатель 00773400102000000</t>
         </is>
       </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -10364,6 +12458,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -10389,6 +12488,11 @@
           <t>Башенная стрела в сборе 00773400400000000</t>
         </is>
       </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -10414,6 +12518,11 @@
           <t>Шасси 00773402810000000</t>
         </is>
       </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -10435,6 +12544,11 @@
           <t>Верхняя стрела в сборе 00773400300000000</t>
         </is>
       </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -10460,6 +12574,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -10485,6 +12604,11 @@
           <t>Консоль 00773400210000000; Верхняя стрела в сборе 00773400300000000; Поворотная платформа 00773400830000000; Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -10510,6 +12634,11 @@
           <t>Верхняя стрела в сборе 00773400300000000; Поворотная платформа 00773400830000000; Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -10535,6 +12664,11 @@
           <t>Поворотная платформа 00773400830000000</t>
         </is>
       </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -10556,6 +12690,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -10577,6 +12716,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -10598,6 +12742,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -10623,6 +12772,11 @@
           <t>Рабочая платформа 00773400110000000</t>
         </is>
       </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -10644,6 +12798,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -10656,8 +12815,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Горизонтальная перегородка 
-буксируемой цепи 27000.12</t>
+          <t>Горизонтальная перегородка буксируемой цепи 27000.12</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
@@ -10666,6 +12824,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -10678,8 +12841,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Вертикальная перегородка 
-буксируемой цепи 35.1</t>
+          <t>Вертикальная перегородка буксируемой цепи 35.1</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
@@ -10688,6 +12850,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -10700,8 +12867,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Соединение каждого звена 
-буксируемой цепи 2700.12.075.0</t>
+          <t>Соединение каждого звена буксируемой цепи 2700.12.075.0</t>
         </is>
       </c>
       <c r="D456" t="inlineStr"/>
@@ -10710,6 +12876,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -10722,8 +12893,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Отверстие соединителя 
-26101.12.C.1</t>
+          <t>Отверстие соединителя 26101.12.C.1</t>
         </is>
       </c>
       <c r="D457" t="inlineStr"/>
@@ -10732,6 +12902,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -10744,8 +12919,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Палец звена соединителя 
-26101.12.C.2</t>
+          <t>Палец звена соединителя 26101.12.C.2</t>
         </is>
       </c>
       <c r="D458" t="inlineStr"/>
@@ -10754,6 +12928,11 @@
           <t>Буксирная система 00773400700000000</t>
         </is>
       </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -10766,8 +12945,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Пневматическая пружина 
-094587</t>
+          <t>Пневматическая пружина 094587</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
@@ -10776,6 +12954,11 @@
           <t>Капот 00773401100000000</t>
         </is>
       </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -10794,7 +12977,12 @@
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Сборка селекторного клапана выравнивания 00773405202200000; Селекторный клапан выдвижения-втягивания в сборе 00773405202400000; Сборка ходового делительного клапана 00773405200800000; Сборка клапан ходового управления 00773405201000000; Селекторный клапан платформы в сборе 00773405201200000</t>
+          <t>Сборка ходового делительного клапана 00773405200800000; Сборка клапан ходового управления 00773405201000000; Селекторный клапан платформы в сборе 00773405201200000; Сборка селекторного клапана выравнивания 00773405202200000; Селекторный клапан выдвижения-втягивания в сборе 00773405202400000</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -10815,7 +13003,12 @@
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773405203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773405203600000; Гидравлический бак в сборе 00773405200200000; Сборка клапан ходового управления 00773405201000000</t>
+          <t>Гидравлический бак в сборе 00773405200200000; Сборка клапан ходового управления 00773405201000000; Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773405203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773405203600000</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -10839,6 +13032,11 @@
           <t>Сборка блока маслоканала 00773405202600000</t>
         </is>
       </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -10857,7 +13055,12 @@
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Селекторный клапан выдвижения-втягивания в сборе 00773405202400000; Селекторный клапан платформы в сборе 00773405201200000</t>
+          <t>Селекторный клапан платформы в сборе 00773405201200000; Селекторный клапан выдвижения-втягивания в сборе 00773405202400000</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -10881,6 +13084,11 @@
           <t>Сборка ходового делительного клапана 00773405200800000</t>
         </is>
       </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -10902,6 +13110,11 @@
           <t>Сборка ходового делительного клапана 00773405200800000</t>
         </is>
       </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -10923,6 +13136,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -10944,6 +13162,11 @@
           <t>Главный клапан в сборе 00773405201600000</t>
         </is>
       </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -10962,7 +13185,12 @@
       <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Сборка блока маслоканала 00773405202600000; Гидравлический бак в сборе 00773405200200000; Сборка ходового делительного клапана 00773405200800000</t>
+          <t>Гидравлический бак в сборе 00773405200200000; Сборка ходового делительного клапана 00773405200800000; Сборка блока маслоканала 00773405202600000</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -10986,6 +13214,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -11007,6 +13240,11 @@
           <t>Сборка блока маслоканала 00773405202600000; Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773405203800000</t>
         </is>
       </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -11028,6 +13266,11 @@
           <t>Гидравлический насос в сборе 00773405200400000</t>
         </is>
       </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -11049,6 +13292,11 @@
           <t>Сборка аварийного насоса с приводом от электродвигателя 00773405202000000</t>
         </is>
       </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -11067,7 +13315,12 @@
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Фильтр высокого давления в сборе 00773405204200000; Главный клапан в сборе 00773405201600000</t>
+          <t>Главный клапан в сборе 00773405201600000; Фильтр высокого давления в сборе 00773405204200000</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -11091,6 +13344,11 @@
           <t>Гидравлический насос в сборе 00773405200400000</t>
         </is>
       </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -11112,6 +13370,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -11129,15 +13392,17 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Интерфейс Х1 для 
-мотора 
-задних 
-колес</t>
+          <t>Интерфейс Х1 для мотора задних колес</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>Сборка ходового мотора 00773405200600000</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -11161,6 +13426,11 @@
           <t>Сборка ходового мотора 00773405200600000</t>
         </is>
       </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -11182,6 +13452,11 @@
           <t>Сборка аварийного насоса с приводом от электродвигателя 00773405202000000</t>
         </is>
       </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -11203,6 +13478,11 @@
           <t>Гидравлический бак в сборе 00773405200200000</t>
         </is>
       </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -11224,6 +13504,11 @@
           <t>Гидравлический насос в сборе 00773405200400000</t>
         </is>
       </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -11242,7 +13527,12 @@
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Балансировочный клапан нижнего гидроцилиндра выравнивания в сборе 00773405202800000; Балансировочный клапан гидроцилиндра консоли в сборе 00773405203200000; Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773405203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773405203600000; Главный клапан в сборе 00773405201600000</t>
+          <t>Главный клапан в сборе 00773405201600000; Балансировочный клапан нижнего гидроцилиндра выравнивания в сборе 00773405202800000; Балансировочный клапан гидроцилиндра консоли в сборе 00773405203200000; Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773405203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773405203600000</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -11266,6 +13556,11 @@
           <t>Гидравлический насос в сборе 00773405200400000</t>
         </is>
       </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -11287,6 +13582,11 @@
           <t>Сборка клапан ходового управления 00773405201000000; Главный клапан в сборе 00773405201600000</t>
         </is>
       </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -11299,21 +13599,22 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Штуцер  колена,  регулируемый 
-по направлению</t>
+          <t>Штуцер  колена,  регулируемый по направлению</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Интерфейс Х1 для 
-мотора 
-передних 
-колес</t>
+          <t>Интерфейс Х1 для мотора передних колес</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>Сборка ходового мотора 00773405200600000</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -11337,6 +13638,11 @@
           <t>Сборка ходового мотора 00773405200600000</t>
         </is>
       </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -11358,6 +13664,11 @@
           <t>Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773405203000000</t>
         </is>
       </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -11379,6 +13690,11 @@
           <t>Сборка ходового мотора 00773405200600000</t>
         </is>
       </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -11400,6 +13716,11 @@
           <t>Сборка фильтра низкого давления 00773405201400000</t>
         </is>
       </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -11421,6 +13742,11 @@
           <t>Гидравлический насос в сборе 00773405200400000</t>
         </is>
       </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -11442,6 +13768,11 @@
           <t>Cистема отвода тепла 00773400106000000; Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -11463,6 +13794,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -11475,10 +13811,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Хомут 
-спирального 
-червяка 
-шайбы</t>
+          <t>Хомут спирального червяка шайбы</t>
         </is>
       </c>
       <c r="D492" t="inlineStr"/>
@@ -11487,6 +13820,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -11499,10 +13837,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Хомут 
-спирального 
-червяка 
-шайбы</t>
+          <t>Хомут спирального червяка шайбы</t>
         </is>
       </c>
       <c r="D493" t="inlineStr"/>
@@ -11511,6 +13846,11 @@
           <t>Cистема отвода тепла 00773400106000000</t>
         </is>
       </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -11532,6 +13872,11 @@
           <t>Впускная система 00773400108000000</t>
         </is>
       </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -11544,8 +13889,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Резиновая  лента  с  пластическим 
-покрытием</t>
+          <t>Резиновая  лента  с  пластическим покрытием</t>
         </is>
       </c>
       <c r="D495" t="inlineStr"/>
@@ -11554,6 +13898,11 @@
           <t>Cистема топлива 00773400104000000</t>
         </is>
       </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -11566,9 +13915,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Документальная 
-коробка 
-355×280×55</t>
+          <t>Документальная коробка 355×280×55</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -11579,6 +13926,11 @@
       <c r="E496" t="inlineStr">
         <is>
           <t>Рабочая платформа 00773400110000000</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>
@@ -11600,6 +13952,11 @@
       <c r="E497" t="inlineStr">
         <is>
           <t>Гидравлический бак в сборе 00773405200200000</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>ZA14J</t>
         </is>
       </c>
     </row>

--- a/Zoomlion/ZA14J.xlsx
+++ b/Zoomlion/ZA14J.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Код материалов</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Наименование и спецификация</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
